--- a/hardware/SPI NAND Flash Breakout Board/v0.1.0/spi_nand_bom (1).xlsx
+++ b/hardware/SPI NAND Flash Breakout Board/v0.1.0/spi_nand_bom (1).xlsx
@@ -8,14 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://emailsc-my.sharepoint.com/personal/dstjohn_email_sc_edu/Documents/Desktop/Edge-Computing-Power-Management-Development-Kit/hardware/SPI NAND Flash Breakout Board/v0.1.0/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="9" documentId="11_5A4B2C90D3AEA2794F446FDFF5D8B87F547F059E" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{586043CD-E287-4552-9B3D-E8241F13E932}"/>
+  <xr:revisionPtr revIDLastSave="20" documentId="11_5A4B2C90D3AEA2794F446FDFF5D8B87F547F059E" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D2820D46-ACB4-4E79-9DC7-D0ECAC4B1347}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="5175" yWindow="8490" windowWidth="21600" windowHeight="12585" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="BOM_3V" sheetId="1" r:id="rId1"/>
     <sheet name="Alt_1V8" sheetId="2" r:id="rId2"/>
     <sheet name="Sheet1" sheetId="3" r:id="rId3"/>
+    <sheet name="JLCPCB" sheetId="4" r:id="rId4"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -35,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="116" uniqueCount="95">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="140" uniqueCount="115">
   <si>
     <t>SPI NAND Carrier Board BOM for NUCLEO-L552ZE-Q</t>
   </si>
@@ -322,6 +323,66 @@
   </si>
   <si>
     <t>TXB0106PWR</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Comment </t>
+  </si>
+  <si>
+    <t>Footprint</t>
+  </si>
+  <si>
+    <t>1uF</t>
+  </si>
+  <si>
+    <t>100nF</t>
+  </si>
+  <si>
+    <t>Conn_01x08_Pin</t>
+  </si>
+  <si>
+    <t>10k</t>
+  </si>
+  <si>
+    <t>TXB0106PW</t>
+  </si>
+  <si>
+    <t>AP2127K-1.8</t>
+  </si>
+  <si>
+    <t>C1,C2,C5</t>
+  </si>
+  <si>
+    <t>C3,C4,C6</t>
+  </si>
+  <si>
+    <t>R1,R2,R3,R4</t>
+  </si>
+  <si>
+    <t>U1</t>
+  </si>
+  <si>
+    <t>U2</t>
+  </si>
+  <si>
+    <t>U3</t>
+  </si>
+  <si>
+    <t>Capacitor_SMD:C_0805_2012Metric</t>
+  </si>
+  <si>
+    <t>Connector_PinSocket_2.54mm:PinSocket_1x08_P2.54mm_Vertical</t>
+  </si>
+  <si>
+    <t>Resistor_SMD:R_0805_2012Metric</t>
+  </si>
+  <si>
+    <t>Breakout:SON127P600X800X80-8N</t>
+  </si>
+  <si>
+    <t>Package_SO:TSSOP-16_4.4x5mm_P0.65mm</t>
+  </si>
+  <si>
+    <t>Package_TO_SOT_SMD:SOT-23-5</t>
   </si>
 </sst>
 </file>
@@ -331,7 +392,7 @@
   <numFmts count="1">
     <numFmt numFmtId="8" formatCode="&quot;$&quot;#,##0.00_);[Red]\(&quot;$&quot;#,##0.00\)"/>
   </numFmts>
-  <fonts count="12">
+  <fonts count="13">
     <font>
       <sz val="11"/>
       <name val="Carlito"/>
@@ -406,6 +467,11 @@
       <family val="2"/>
       <scheme val="major"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <name val="Carlito"/>
+    </font>
   </fonts>
   <fills count="7">
     <fill>
@@ -453,25 +519,13 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -489,6 +543,19 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="8" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -505,6 +572,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -670,32 +741,32 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="24" customHeight="1">
-      <c r="A1" s="3" t="s">
+      <c r="A1" s="12" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="3"/>
-      <c r="C1" s="3"/>
-      <c r="D1" s="3"/>
-      <c r="E1" s="3"/>
-      <c r="F1" s="3"/>
-      <c r="G1" s="3"/>
-      <c r="H1" s="3"/>
-      <c r="I1" s="3"/>
-      <c r="J1" s="3"/>
+      <c r="B1" s="12"/>
+      <c r="C1" s="12"/>
+      <c r="D1" s="12"/>
+      <c r="E1" s="12"/>
+      <c r="F1" s="12"/>
+      <c r="G1" s="12"/>
+      <c r="H1" s="12"/>
+      <c r="I1" s="12"/>
+      <c r="J1" s="12"/>
     </row>
     <row r="2" spans="1:10" ht="32.1" customHeight="1">
-      <c r="A2" s="4" t="s">
+      <c r="A2" s="13" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="4"/>
-      <c r="C2" s="4"/>
-      <c r="D2" s="4"/>
-      <c r="E2" s="4"/>
-      <c r="F2" s="4"/>
-      <c r="G2" s="4"/>
-      <c r="H2" s="4"/>
-      <c r="I2" s="4"/>
-      <c r="J2" s="4"/>
+      <c r="B2" s="13"/>
+      <c r="C2" s="13"/>
+      <c r="D2" s="13"/>
+      <c r="E2" s="13"/>
+      <c r="F2" s="13"/>
+      <c r="G2" s="13"/>
+      <c r="H2" s="13"/>
+      <c r="I2" s="13"/>
+      <c r="J2" s="13"/>
     </row>
     <row r="4" spans="1:10" ht="33.950000000000003" customHeight="1">
       <c r="A4" s="1" t="s">
@@ -1018,18 +1089,18 @@
       </c>
     </row>
     <row r="16" spans="1:10" ht="27.95" customHeight="1">
-      <c r="A16" s="5" t="s">
+      <c r="A16" s="14" t="s">
         <v>73</v>
       </c>
-      <c r="B16" s="5"/>
-      <c r="C16" s="5"/>
-      <c r="D16" s="5"/>
-      <c r="E16" s="5"/>
-      <c r="F16" s="5"/>
-      <c r="G16" s="5"/>
-      <c r="H16" s="5"/>
-      <c r="I16" s="5"/>
-      <c r="J16" s="5"/>
+      <c r="B16" s="14"/>
+      <c r="C16" s="14"/>
+      <c r="D16" s="14"/>
+      <c r="E16" s="14"/>
+      <c r="F16" s="14"/>
+      <c r="G16" s="14"/>
+      <c r="H16" s="14"/>
+      <c r="I16" s="14"/>
+      <c r="J16" s="14"/>
     </row>
   </sheetData>
   <mergeCells count="3">
@@ -1055,24 +1126,24 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="24" customHeight="1">
-      <c r="A1" s="6" t="s">
+      <c r="A1" s="15" t="s">
         <v>74</v>
       </c>
-      <c r="B1" s="6"/>
-      <c r="C1" s="6"/>
-      <c r="D1" s="6"/>
-      <c r="E1" s="6"/>
-      <c r="F1" s="6"/>
+      <c r="B1" s="15"/>
+      <c r="C1" s="15"/>
+      <c r="D1" s="15"/>
+      <c r="E1" s="15"/>
+      <c r="F1" s="15"/>
     </row>
     <row r="2" spans="1:6" ht="33.950000000000003" customHeight="1">
-      <c r="A2" s="4" t="s">
+      <c r="A2" s="13" t="s">
         <v>75</v>
       </c>
-      <c r="B2" s="4"/>
-      <c r="C2" s="4"/>
-      <c r="D2" s="4"/>
-      <c r="E2" s="4"/>
-      <c r="F2" s="4"/>
+      <c r="B2" s="13"/>
+      <c r="C2" s="13"/>
+      <c r="D2" s="13"/>
+      <c r="E2" s="13"/>
+      <c r="F2" s="13"/>
     </row>
     <row r="4" spans="1:6" ht="26.1" customHeight="1">
       <c r="A4" s="1" t="s">
@@ -1153,57 +1224,57 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="15">
-      <c r="A1" s="7" t="s">
+      <c r="A1" s="3" t="s">
         <v>81</v>
       </c>
-      <c r="B1" s="7" t="s">
+      <c r="B1" s="3" t="s">
         <v>82</v>
       </c>
-      <c r="C1" s="7" t="s">
+      <c r="C1" s="3" t="s">
         <v>83</v>
       </c>
-      <c r="D1" s="7" t="s">
+      <c r="D1" s="3" t="s">
         <v>84</v>
       </c>
-      <c r="E1" s="7" t="s">
+      <c r="E1" s="3" t="s">
         <v>85</v>
       </c>
-      <c r="F1" s="7" t="s">
+      <c r="F1" s="3" t="s">
         <v>86</v>
       </c>
-      <c r="G1" s="7" t="s">
+      <c r="G1" s="3" t="s">
         <v>87</v>
       </c>
-      <c r="H1" s="7" t="s">
+      <c r="H1" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="I1" s="7" t="s">
+      <c r="I1" s="3" t="s">
         <v>88</v>
       </c>
-      <c r="J1" s="7" t="s">
+      <c r="J1" s="3" t="s">
         <v>89</v>
       </c>
-      <c r="K1" s="7" t="s">
+      <c r="K1" s="3" t="s">
         <v>90</v>
       </c>
-      <c r="L1" s="7" t="s">
+      <c r="L1" s="3" t="s">
         <v>91</v>
       </c>
     </row>
     <row r="2" spans="1:12" ht="15">
-      <c r="A2" s="8"/>
-      <c r="B2" s="9" t="s">
+      <c r="A2" s="4"/>
+      <c r="B2" s="5" t="s">
         <v>94</v>
       </c>
-      <c r="C2" s="10" t="s">
+      <c r="C2" s="6" t="s">
         <v>94</v>
       </c>
-      <c r="D2" s="8"/>
-      <c r="E2" s="11"/>
-      <c r="F2" s="12"/>
-      <c r="G2" s="12"/>
-      <c r="H2" s="8"/>
-      <c r="I2" s="13" t="s">
+      <c r="D2" s="4"/>
+      <c r="E2" s="7"/>
+      <c r="F2" s="8"/>
+      <c r="G2" s="8"/>
+      <c r="H2" s="4"/>
+      <c r="I2" s="9" t="s">
         <v>93</v>
       </c>
       <c r="J2" t="s">
@@ -1211,51 +1282,154 @@
       </c>
     </row>
     <row r="3" spans="1:12" ht="15">
-      <c r="A3" s="8"/>
-      <c r="B3" s="9"/>
-      <c r="C3" s="9"/>
-      <c r="D3" s="8"/>
-      <c r="E3" s="11"/>
-      <c r="F3" s="14"/>
-      <c r="G3" s="14"/>
-      <c r="H3" s="8"/>
-      <c r="I3" s="13"/>
+      <c r="A3" s="4"/>
+      <c r="B3" s="5"/>
+      <c r="C3" s="5"/>
+      <c r="D3" s="4"/>
+      <c r="E3" s="7"/>
+      <c r="F3" s="10"/>
+      <c r="G3" s="10"/>
+      <c r="H3" s="4"/>
+      <c r="I3" s="9"/>
     </row>
     <row r="4" spans="1:12" ht="15">
-      <c r="A4" s="8"/>
-      <c r="B4" s="8"/>
-      <c r="C4" s="8"/>
-      <c r="D4" s="8"/>
-      <c r="E4" s="8"/>
-      <c r="F4" s="8"/>
-      <c r="G4" s="8"/>
-      <c r="H4" s="8"/>
-      <c r="I4" s="8"/>
+      <c r="A4" s="4"/>
+      <c r="B4" s="4"/>
+      <c r="C4" s="4"/>
+      <c r="D4" s="4"/>
+      <c r="E4" s="4"/>
+      <c r="F4" s="4"/>
+      <c r="G4" s="4"/>
+      <c r="H4" s="4"/>
+      <c r="I4" s="4"/>
     </row>
     <row r="5" spans="1:12" ht="15">
-      <c r="A5" s="8"/>
-      <c r="B5" s="8"/>
-      <c r="C5" s="8"/>
-      <c r="D5" s="8"/>
-      <c r="E5" s="8"/>
-      <c r="F5" s="8"/>
-      <c r="G5" s="8"/>
-      <c r="H5" s="8"/>
-      <c r="I5" s="8"/>
+      <c r="A5" s="4"/>
+      <c r="B5" s="4"/>
+      <c r="C5" s="4"/>
+      <c r="D5" s="4"/>
+      <c r="E5" s="4"/>
+      <c r="F5" s="4"/>
+      <c r="G5" s="4"/>
+      <c r="H5" s="4"/>
+      <c r="I5" s="4"/>
     </row>
     <row r="6" spans="1:12" ht="15">
-      <c r="A6" s="8"/>
-      <c r="B6" s="8"/>
-      <c r="C6" s="8"/>
-      <c r="D6" s="8"/>
-      <c r="E6" s="8"/>
-      <c r="F6" s="8"/>
-      <c r="G6" s="8"/>
-      <c r="H6" s="8"/>
-      <c r="I6" s="8"/>
+      <c r="A6" s="4"/>
+      <c r="B6" s="4"/>
+      <c r="C6" s="4"/>
+      <c r="D6" s="4"/>
+      <c r="E6" s="4"/>
+      <c r="F6" s="4"/>
+      <c r="G6" s="4"/>
+      <c r="H6" s="4"/>
+      <c r="I6" s="4"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7856D750-8709-4059-BB67-118BDB84F0EC}">
+  <dimension ref="A1:C8"/>
+  <sheetFormatPr defaultRowHeight="14.25"/>
+  <cols>
+    <col min="1" max="1" width="20.125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="57.375" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" s="11" customFormat="1" ht="15">
+      <c r="A1" s="11" t="s">
+        <v>95</v>
+      </c>
+      <c r="B1" s="11" t="s">
+        <v>81</v>
+      </c>
+      <c r="C1" s="11" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3">
+      <c r="A2" t="s">
+        <v>97</v>
+      </c>
+      <c r="B2" t="s">
+        <v>103</v>
+      </c>
+      <c r="C2" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3">
+      <c r="A3" t="s">
+        <v>98</v>
+      </c>
+      <c r="B3" t="s">
+        <v>104</v>
+      </c>
+      <c r="C3" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3">
+      <c r="A4" t="s">
+        <v>99</v>
+      </c>
+      <c r="B4" t="s">
+        <v>58</v>
+      </c>
+      <c r="C4" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3">
+      <c r="A5" t="s">
+        <v>100</v>
+      </c>
+      <c r="B5" t="s">
+        <v>105</v>
+      </c>
+      <c r="C5" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3">
+      <c r="A6" t="s">
+        <v>77</v>
+      </c>
+      <c r="B6" t="s">
+        <v>106</v>
+      </c>
+      <c r="C6" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3">
+      <c r="A7" t="s">
+        <v>101</v>
+      </c>
+      <c r="B7" t="s">
+        <v>107</v>
+      </c>
+      <c r="C7" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3">
+      <c r="A8" t="s">
+        <v>102</v>
+      </c>
+      <c r="B8" t="s">
+        <v>108</v>
+      </c>
+      <c r="C8" t="s">
+        <v>114</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>